--- a/data/b2_candoi/B2 Candói 04-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 04-2026.xlsx
@@ -4739,20 +4739,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1378.92</v>
+        <v>57597.49</v>
       </c>
     </row>
     <row r="3">
@@ -4761,70 +4761,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57246.9</v>
+        <v>2634.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2537.54</v>
+        <v>2445.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>837.75</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3200</v>
+        <v>692.47</v>
       </c>
     </row>
     <row r="7">
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3809.25</v>
+        <v>3585.89</v>
       </c>
     </row>
     <row r="8">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1036.25</v>
+        <v>885.63</v>
       </c>
     </row>
     <row r="9">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>7933.79</v>
+        <v>7624.03</v>
       </c>
     </row>
     <row r="10">
@@ -4896,97 +4896,97 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1040.27</v>
+        <v>992.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46130</v>
+        <v>46128</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1109.1</v>
+        <v>1805.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46131</v>
+        <v>46129</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3525.07</v>
+        <v>1071.94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46132</v>
+        <v>46131</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>20237.34</v>
+        <v>3716.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2285.75</v>
+        <v>20249.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2295.28</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="16">
@@ -4995,16 +4995,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>7920</v>
+        <v>1101.82</v>
       </c>
     </row>
     <row r="17">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3585.06</v>
+        <v>3819.03</v>
       </c>
     </row>
     <row r="18">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2062.09</v>
+        <v>1925.89</v>
       </c>
     </row>
   </sheetData>
